--- a/api/xlsx/en/SectorCategory.xlsx
+++ b/api/xlsx/en/SectorCategory.xlsx
@@ -268,7 +268,7 @@
     <t>520</t>
   </si>
   <si>
-    <t>Developmental Food Aid/Food Security Assistance</t>
+    <t>Development Food Assistance</t>
   </si>
   <si>
     <t>530</t>

--- a/api/xlsx/en/SectorCategory.xlsx
+++ b/api/xlsx/en/SectorCategory.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="110">
   <si>
     <t>code</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>status</t>
+  </si>
+  <si>
+    <t>public-database</t>
   </si>
   <si>
     <t>111</t>
@@ -672,10 +675,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -694,528 +697,531 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F20" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F23" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F24" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F26" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F28" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F29" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F32" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C33" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F33" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F34" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F35" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F36" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F37" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F38" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B39" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F39" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B40" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C40" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F40" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B41" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C41" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F41" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F42" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B43" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F44" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B45" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C45" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F45" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorCategory.xlsx
+++ b/api/xlsx/en/SectorCategory.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="109">
   <si>
     <t>code</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>status</t>
-  </si>
-  <si>
-    <t>public-database</t>
   </si>
   <si>
     <t>111</t>
@@ -675,10 +672,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -697,531 +694,528 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
       <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" t="s">
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
         <v>24</v>
       </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>25</v>
       </c>
-      <c r="B10" t="s">
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
         <v>26</v>
       </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>27</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>28</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
         <v>29</v>
       </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>31</v>
       </c>
-      <c r="C12" t="s">
+      <c r="F12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
         <v>32</v>
       </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>33</v>
       </c>
-      <c r="B13" t="s">
+      <c r="F13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
         <v>34</v>
       </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>35</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>36</v>
       </c>
-      <c r="C14" t="s">
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
         <v>37</v>
       </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>38</v>
       </c>
-      <c r="B15" t="s">
+      <c r="F15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
         <v>39</v>
       </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>40</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>41</v>
       </c>
-      <c r="C16" t="s">
+      <c r="F16" t="s">
         <v>42</v>
-      </c>
-      <c r="F16" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
         <v>44</v>
       </c>
-      <c r="B17" t="s">
-        <v>45</v>
-      </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" t="s">
         <v>46</v>
       </c>
-      <c r="B18" t="s">
-        <v>47</v>
-      </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
         <v>48</v>
       </c>
-      <c r="B19" t="s">
-        <v>49</v>
-      </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" t="s">
         <v>50</v>
       </c>
-      <c r="B20" t="s">
-        <v>51</v>
-      </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" t="s">
         <v>52</v>
       </c>
-      <c r="B21" t="s">
-        <v>53</v>
-      </c>
       <c r="F21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" t="s">
         <v>54</v>
       </c>
-      <c r="B22" t="s">
-        <v>55</v>
-      </c>
       <c r="F22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" t="s">
         <v>56</v>
       </c>
-      <c r="B23" t="s">
-        <v>57</v>
-      </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" t="s">
         <v>58</v>
       </c>
-      <c r="B24" t="s">
-        <v>59</v>
-      </c>
       <c r="F24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" t="s">
         <v>60</v>
       </c>
-      <c r="B25" t="s">
-        <v>61</v>
-      </c>
       <c r="F25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" t="s">
         <v>62</v>
       </c>
-      <c r="B26" t="s">
-        <v>63</v>
-      </c>
       <c r="F26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" t="s">
         <v>64</v>
       </c>
-      <c r="B27" t="s">
-        <v>65</v>
-      </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" t="s">
         <v>66</v>
       </c>
-      <c r="B28" t="s">
-        <v>67</v>
-      </c>
       <c r="F28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" t="s">
         <v>68</v>
       </c>
-      <c r="B29" t="s">
-        <v>69</v>
-      </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" t="s">
         <v>70</v>
       </c>
-      <c r="B30" t="s">
-        <v>71</v>
-      </c>
       <c r="F30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" t="s">
         <v>72</v>
       </c>
-      <c r="B31" t="s">
-        <v>73</v>
-      </c>
       <c r="F31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" t="s">
         <v>74</v>
       </c>
-      <c r="B32" t="s">
-        <v>75</v>
-      </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" t="s">
         <v>76</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>77</v>
       </c>
-      <c r="C33" t="s">
-        <v>78</v>
-      </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" t="s">
         <v>79</v>
       </c>
-      <c r="B34" t="s">
-        <v>80</v>
-      </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" t="s">
         <v>81</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>82</v>
       </c>
-      <c r="C35" t="s">
-        <v>83</v>
-      </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" t="s">
         <v>84</v>
       </c>
-      <c r="B36" t="s">
-        <v>85</v>
-      </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" t="s">
         <v>86</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>87</v>
       </c>
-      <c r="C37" t="s">
-        <v>88</v>
-      </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" t="s">
         <v>89</v>
       </c>
-      <c r="B38" t="s">
-        <v>90</v>
-      </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" t="s">
         <v>91</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>92</v>
       </c>
-      <c r="C39" t="s">
-        <v>93</v>
-      </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" t="s">
         <v>94</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>95</v>
       </c>
-      <c r="C40" t="s">
-        <v>96</v>
-      </c>
       <c r="F40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" t="s">
         <v>97</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>98</v>
       </c>
-      <c r="C41" t="s">
-        <v>99</v>
-      </c>
       <c r="F41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" t="s">
         <v>100</v>
       </c>
-      <c r="B42" t="s">
-        <v>101</v>
-      </c>
       <c r="F42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
+        <v>101</v>
+      </c>
+      <c r="B43" t="s">
         <v>102</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>103</v>
       </c>
-      <c r="C43" t="s">
-        <v>104</v>
-      </c>
       <c r="F43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" t="s">
         <v>105</v>
       </c>
-      <c r="B44" t="s">
-        <v>106</v>
-      </c>
       <c r="F44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
+        <v>106</v>
+      </c>
+      <c r="B45" t="s">
         <v>107</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>108</v>
       </c>
-      <c r="C45" t="s">
-        <v>109</v>
-      </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorCategory.xlsx
+++ b/api/xlsx/en/SectorCategory.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="107">
   <si>
     <t>code</t>
   </si>
@@ -23,12 +23,6 @@
   </si>
   <si>
     <t>description</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>url</t>
   </si>
   <si>
     <t>status</t>
@@ -672,10 +666,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -688,534 +682,528 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>21</v>
       </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>23</v>
       </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
         <v>24</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>25</v>
       </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
+      <c r="C11" t="s">
         <v>26</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
         <v>27</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B12" t="s">
         <v>28</v>
       </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
+      <c r="C12" t="s">
         <v>29</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
         <v>30</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B13" t="s">
         <v>31</v>
       </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
         <v>32</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>33</v>
       </c>
-      <c r="F13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
+      <c r="C14" t="s">
         <v>34</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
         <v>35</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B15" t="s">
         <v>36</v>
       </c>
-      <c r="F14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
         <v>37</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>38</v>
       </c>
-      <c r="F15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
+      <c r="C16" t="s">
         <v>39</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" t="s">
         <v>40</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
         <v>41</v>
       </c>
-      <c r="F16" t="s">
+      <c r="B17" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>44</v>
       </c>
-      <c r="F17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
         <v>45</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>46</v>
       </c>
-      <c r="F18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
         <v>47</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>48</v>
       </c>
-      <c r="F19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
         <v>49</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>50</v>
       </c>
-      <c r="F20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
+      <c r="D21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
         <v>51</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>52</v>
       </c>
-      <c r="F21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
         <v>53</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>54</v>
       </c>
-      <c r="F22" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
+      <c r="D23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
         <v>55</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B24" t="s">
         <v>56</v>
       </c>
-      <c r="F23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" t="s">
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
         <v>57</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>58</v>
       </c>
-      <c r="F24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
+      <c r="D25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
         <v>59</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>60</v>
       </c>
-      <c r="F25" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" t="s">
+      <c r="D26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
         <v>61</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>62</v>
       </c>
-      <c r="F26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" t="s">
+      <c r="D27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
         <v>63</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>64</v>
       </c>
-      <c r="F27" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" t="s">
+      <c r="D28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
         <v>65</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>66</v>
       </c>
-      <c r="F28" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" t="s">
+      <c r="D29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
         <v>67</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>68</v>
       </c>
-      <c r="F29" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" t="s">
+      <c r="D30" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
         <v>69</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>70</v>
       </c>
-      <c r="F30" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" t="s">
+      <c r="D31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
         <v>71</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" t="s">
         <v>72</v>
       </c>
-      <c r="F31" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
+      <c r="D32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
         <v>73</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>74</v>
       </c>
-      <c r="F32" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" t="s">
+      <c r="C33" t="s">
         <v>75</v>
       </c>
-      <c r="B33" t="s">
+      <c r="D33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
         <v>76</v>
       </c>
-      <c r="C33" t="s">
+      <c r="B34" t="s">
         <v>77</v>
       </c>
-      <c r="F33" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" t="s">
+      <c r="D34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
         <v>78</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>79</v>
       </c>
-      <c r="F34" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" t="s">
+      <c r="C35" t="s">
         <v>80</v>
       </c>
-      <c r="B35" t="s">
+      <c r="D35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
         <v>81</v>
       </c>
-      <c r="C35" t="s">
+      <c r="B36" t="s">
         <v>82</v>
       </c>
-      <c r="F35" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" t="s">
+      <c r="D36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
         <v>83</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>84</v>
       </c>
-      <c r="F36" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" t="s">
+      <c r="C37" t="s">
         <v>85</v>
       </c>
-      <c r="B37" t="s">
+      <c r="D37" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
         <v>86</v>
       </c>
-      <c r="C37" t="s">
+      <c r="B38" t="s">
         <v>87</v>
       </c>
-      <c r="F37" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" t="s">
+      <c r="D38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
         <v>88</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>89</v>
       </c>
-      <c r="F38" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" t="s">
+      <c r="C39" t="s">
         <v>90</v>
       </c>
-      <c r="B39" t="s">
+      <c r="D39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
         <v>91</v>
       </c>
-      <c r="C39" t="s">
+      <c r="B40" t="s">
         <v>92</v>
       </c>
-      <c r="F39" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" t="s">
+      <c r="C40" t="s">
         <v>93</v>
       </c>
-      <c r="B40" t="s">
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
         <v>94</v>
       </c>
-      <c r="C40" t="s">
+      <c r="B41" t="s">
         <v>95</v>
       </c>
-      <c r="F40" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" t="s">
+      <c r="C41" t="s">
         <v>96</v>
       </c>
-      <c r="B41" t="s">
+      <c r="D41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
         <v>97</v>
       </c>
-      <c r="C41" t="s">
+      <c r="B42" t="s">
         <v>98</v>
       </c>
-      <c r="F41" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" t="s">
+      <c r="D42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
         <v>99</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
         <v>100</v>
       </c>
-      <c r="F42" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" t="s">
+      <c r="C43" t="s">
         <v>101</v>
       </c>
-      <c r="B43" t="s">
+      <c r="D43" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
         <v>102</v>
       </c>
-      <c r="C43" t="s">
+      <c r="B44" t="s">
         <v>103</v>
       </c>
-      <c r="F43" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" t="s">
+      <c r="D44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
         <v>104</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B45" t="s">
         <v>105</v>
       </c>
-      <c r="F44" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" t="s">
+      <c r="C45" t="s">
         <v>106</v>
       </c>
-      <c r="B45" t="s">
-        <v>107</v>
-      </c>
-      <c r="C45" t="s">
-        <v>108</v>
-      </c>
-      <c r="F45" t="s">
-        <v>9</v>
+      <c r="D45" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/api/xlsx/en/SectorCategory.xlsx
+++ b/api/xlsx/en/SectorCategory.xlsx
@@ -304,7 +304,7 @@
     <t>Disaster Prevention &amp; Preparedness</t>
   </si>
   <si>
-    <t>See codes 41050 and 15220 for prevention of floods and conflicts.</t>
+    <t>See code 43060 for disaster risk reduction.</t>
   </si>
   <si>
     <t>910</t>
